--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD0E29E-0F79-4347-80D5-9EDB263F78C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C79CB2D-4260-4191-AFB6-76181955FEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9135" yWindow="675" windowWidth="20790" windowHeight="14580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1305" yWindow="555" windowWidth="20790" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -105,6 +105,34 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -497,14 +525,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -575,14 +603,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.1875</v>
+        <v>0.47916666666666669</v>
       </c>
     </row>
   </sheetData>
@@ -599,7 +627,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1018,17 +1046,35 @@
         <f t="shared" ref="A70:A102" si="1">A69+1</f>
         <v>68</v>
       </c>
+      <c r="B70" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:13">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
+      <c r="B71" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:13">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
       </c>
       <c r="M72" t="s">
         <v>7</v>
@@ -1360,7 +1406,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1745,100 +1791,118 @@
         <v>162</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:3">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:3">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
-    </row>
-    <row r="79" spans="1:1">
+      <c r="B78" t="s">
+        <v>21</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
-    </row>
-    <row r="80" spans="1:1">
+      <c r="B79" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
+      </c>
+      <c r="B80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1846,12 +1910,24 @@
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
+      <c r="B81" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
+      <c r="B82" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
@@ -1978,59 +2054,119 @@
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
+      <c r="B93" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
+      <c r="B94" t="s">
+        <v>19</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
+      <c r="B95" t="s">
+        <v>20</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
+      <c r="B96" t="s">
+        <v>21</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
+      <c r="B97" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
-    </row>
-    <row r="99" spans="1:1">
+      <c r="B98" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
-    </row>
-    <row r="100" spans="1:1">
+      <c r="B99" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
-    </row>
-    <row r="101" spans="1:1">
+      <c r="B100" t="s">
+        <v>19</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
-    </row>
-    <row r="102" spans="1:1">
+      <c r="B101" t="s">
+        <v>20</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
+      </c>
+      <c r="B102" t="s">
+        <v>21</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C79CB2D-4260-4191-AFB6-76181955FEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB300C0-CCF6-4F6F-8A71-77537074213A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1305" yWindow="555" windowWidth="20790" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6300" yWindow="1185" windowWidth="20790" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="26">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -129,6 +129,22 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -541,14 +557,14 @@
       </c>
       <c r="C6">
         <f>SUM(listening!C73:C102)</f>
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>0.56666666666666665</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -603,14 +619,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.47916666666666669</v>
+        <v>0.6875</v>
       </c>
     </row>
   </sheetData>
@@ -627,7 +643,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1337,53 +1353,107 @@
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
+      <c r="B94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
+      <c r="B95" t="s">
+        <v>23</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
+      <c r="B96" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
+      <c r="B97" t="s">
+        <v>22</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-    </row>
-    <row r="99" spans="1:1">
+      <c r="B98" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
-    </row>
-    <row r="100" spans="1:1">
+      <c r="B99" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
-    </row>
-    <row r="101" spans="1:1">
+      <c r="B100" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
-    </row>
-    <row r="102" spans="1:1">
+      <c r="B101" t="s">
+        <v>23</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>100</v>
+      </c>
+      <c r="B102" t="s">
+        <v>25</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1406,7 +1476,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1808,11 +1878,23 @@
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
+      <c r="B67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
+      </c>
+      <c r="B68" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1820,53 +1902,107 @@
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
       </c>
+      <c r="B69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
+      <c r="B71" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
+      <c r="B72" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
+      <c r="B74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
+      <c r="B75" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
+      </c>
+      <c r="B77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:3">

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB300C0-CCF6-4F6F-8A71-77537074213A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BF4804-E17B-4D48-85B4-711EE6297FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6300" yWindow="1185" windowWidth="20790" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="300" windowWidth="16215" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="30">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -153,6 +153,22 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -509,14 +525,14 @@
       </c>
       <c r="C3">
         <f>SUM(listening!C3:C12)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>10</v>
       </c>
       <c r="E3" s="1">
         <f>C3/D3</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -587,14 +603,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -643,7 +659,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -661,10 +677,22 @@
       <c r="A3">
         <v>1</v>
       </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
         <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -672,47 +700,95 @@
         <f>A4+1</f>
         <v>3</v>
       </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
         <f t="shared" ref="A6:A69" si="0">A5+1</f>
         <v>4</v>
       </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1476,7 +1552,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1493,6 +1569,12 @@
     <row r="3" spans="1:3">
       <c r="A3">
         <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1500,53 +1582,107 @@
         <f>A3+1</f>
         <v>102</v>
       </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
         <f t="shared" ref="A5:A68" si="0">A4+1</f>
         <v>103</v>
       </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3">

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BF4804-E17B-4D48-85B4-711EE6297FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23439E7E-E5DE-4ADB-B7A9-FC7192AA5F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="300" windowWidth="16215" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7035" yWindow="720" windowWidth="16215" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="38">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -169,6 +169,37 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -541,14 +572,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -603,14 +634,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.2</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -659,7 +690,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -796,116 +827,176 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1552,7 +1643,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1690,116 +1781,176 @@
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23439E7E-E5DE-4ADB-B7A9-FC7192AA5F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69532672-3422-44A0-89DD-B6582F5CC52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7035" yWindow="720" windowWidth="16215" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15750" yWindow="765" windowWidth="16215" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="44">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -200,6 +200,28 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -572,14 +594,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0.3</v>
+        <v>0.56666666666666665</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -634,14 +656,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.375</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -690,7 +712,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -947,59 +969,119 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
+      <c r="B26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
+      <c r="B29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -1643,7 +1725,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1901,59 +1983,119 @@
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
+      <c r="B28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>
+      </c>
+      <c r="B32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:1">

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69532672-3422-44A0-89DD-B6582F5CC52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFCA498-D46A-4195-8301-4A815CE039C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15750" yWindow="765" windowWidth="16215" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="885" yWindow="615" windowWidth="16215" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="48">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -222,6 +222,22 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -594,14 +610,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0.56666666666666665</v>
+        <v>0.76666666666666672</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -656,14 +672,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.55000000000000004</v>
+        <v>0.67500000000000004</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -712,7 +728,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1084,97 +1100,157 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="B42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -1725,7 +1801,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2098,97 +2174,157 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="B42" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFCA498-D46A-4195-8301-4A815CE039C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630ABBFE-A4C6-4F49-A213-751587F56A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="885" yWindow="615" windowWidth="16215" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="675" yWindow="0" windowWidth="11985" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="52">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -238,6 +238,22 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -626,14 +642,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.46666666666666667</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -704,14 +720,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.6875</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
   </sheetData>
@@ -728,7 +744,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1225,128 +1241,200 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
+      <c r="B43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
+      <c r="B44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
+      <c r="B45" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
+      <c r="B46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
+      <c r="B47" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="B48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50" t="s">
+        <v>50</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="B51" t="s">
+        <v>48</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="B52" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
+      <c r="B53" t="s">
+        <v>50</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
+      <c r="B54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -1801,7 +1889,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2330,100 +2418,160 @@
         <v>146</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
-    </row>
-    <row r="56" spans="1:1">
+      <c r="B55" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
-    </row>
-    <row r="57" spans="1:1">
+      <c r="B56" t="s">
+        <v>50</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
-    </row>
-    <row r="58" spans="1:1">
+      <c r="B57" t="s">
+        <v>49</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
-    </row>
-    <row r="59" spans="1:1">
+      <c r="B58" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
-    </row>
-    <row r="60" spans="1:1">
+      <c r="B59" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
-    </row>
-    <row r="61" spans="1:1">
+      <c r="B60" t="s">
+        <v>50</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
-    </row>
-    <row r="62" spans="1:1">
+      <c r="B61" t="s">
+        <v>49</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-    </row>
-    <row r="63" spans="1:1">
+      <c r="B62" t="s">
+        <v>51</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
-    </row>
-    <row r="64" spans="1:1">
+      <c r="B63" t="s">
+        <v>51</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>
+      </c>
+      <c r="B64" t="s">
+        <v>50</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -2431,11 +2579,23 @@
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
+      <c r="B65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
+      </c>
+      <c r="B66" t="s">
+        <v>50</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:3">

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630ABBFE-A4C6-4F49-A213-751587F56A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E80342-746E-4A8E-9FA8-B4022474CE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="0" windowWidth="11985" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="375" yWindow="120" windowWidth="22125" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="56">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -254,6 +254,22 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -642,14 +658,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0.46666666666666667</v>
+        <v>0.76666666666666672</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -704,14 +720,14 @@
       </c>
       <c r="C10">
         <f>SUM(reading!C43:C54)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -744,7 +760,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1385,53 +1401,107 @@
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
+      <c r="B55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
+      <c r="B56" t="s">
+        <v>52</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
+      <c r="B57" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
+      <c r="B58" t="s">
+        <v>54</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
+      <c r="B59" t="s">
+        <v>55</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
+      <c r="B60" t="s">
+        <v>52</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
+      <c r="B61" t="s">
+        <v>52</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
+      <c r="B62" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1889,7 +1959,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2387,35 +2457,71 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
+      <c r="B43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
+      <c r="B44" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
+      <c r="B45" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
+      <c r="B46" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
+      <c r="B47" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
+      </c>
+      <c r="B48" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:3">

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E80342-746E-4A8E-9FA8-B4022474CE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEBBB5C-002C-429B-B5A7-8A238A33D0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="375" yWindow="120" windowWidth="22125" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="285" yWindow="450" windowWidth="15780" windowHeight="14955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="60">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -270,6 +270,22 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -658,14 +674,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0.76666666666666672</v>
+        <v>0.96666666666666667</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -720,14 +736,14 @@
       </c>
       <c r="C10">
         <f>SUM(reading!C43:C54)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.58333333333333337</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -760,7 +776,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1509,35 +1525,71 @@
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
+      <c r="B64" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:13">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
+      <c r="B65" t="s">
+        <v>57</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:13">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
+      <c r="B66" t="s">
+        <v>58</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:13">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
+      <c r="B67" t="s">
+        <v>57</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:13">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
+      <c r="B68" t="s">
+        <v>56</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:13">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -1959,7 +2011,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2529,35 +2581,71 @@
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
+      <c r="B50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
+      <c r="B51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
+      <c r="B52" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
+      <c r="B53" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
+      </c>
+      <c r="B54" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3">

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEBBB5C-002C-429B-B5A7-8A238A33D0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{170A8442-CEAA-4730-9A40-8967AA9214DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="450" windowWidth="15780" windowHeight="14955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13305" yWindow="345" windowWidth="15780" windowHeight="14955" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="60">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -309,18 +309,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -335,10 +329,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -770,6 +763,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -790,7 +784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" hidden="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -801,7 +795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" hidden="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -812,7 +806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" hidden="1">
       <c r="A5">
         <f>A4+1</f>
         <v>3</v>
@@ -824,7 +818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" hidden="1">
       <c r="A6">
         <f t="shared" ref="A6:A69" si="0">A5+1</f>
         <v>4</v>
@@ -836,7 +830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" hidden="1">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -848,7 +842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" hidden="1">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -860,7 +854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" hidden="1">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -872,7 +866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" hidden="1">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -884,7 +878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" hidden="1">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -896,7 +890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" hidden="1">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -908,7 +902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" hidden="1">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -920,7 +914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" hidden="1">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -932,7 +926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" hidden="1">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -944,7 +938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" hidden="1">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -956,7 +950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" hidden="1">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -968,7 +962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" hidden="1">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -992,7 +986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" hidden="1">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1004,7 +998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" hidden="1">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1016,7 +1010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" hidden="1">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1028,7 +1022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" hidden="1">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1052,7 +1046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" hidden="1">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1064,7 +1058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" hidden="1">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1088,7 +1082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" hidden="1">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1100,7 +1094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" hidden="1">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1112,7 +1106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" hidden="1">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1124,7 +1118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" hidden="1">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1136,7 +1130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" hidden="1">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1148,7 +1142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" hidden="1">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -1172,7 +1166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" hidden="1">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -1184,7 +1178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" hidden="1">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -1220,7 +1214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" hidden="1">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -1232,7 +1226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" hidden="1">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -1256,7 +1250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" hidden="1">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -1268,7 +1262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" hidden="1">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -1280,7 +1274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" hidden="1">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -1292,7 +1286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" hidden="1">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -1304,7 +1298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" hidden="1">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -1316,7 +1310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" hidden="1">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -1328,7 +1322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" hidden="1">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -1340,7 +1334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" hidden="1">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -1364,7 +1358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" hidden="1">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -1376,7 +1370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" hidden="1">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -1388,7 +1382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" hidden="1">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -1400,7 +1394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" hidden="1">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -1412,7 +1406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" hidden="1">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -1424,7 +1418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" hidden="1">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -1436,7 +1430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" hidden="1">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -1448,7 +1442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" hidden="1">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -1460,7 +1454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" hidden="1">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -1472,7 +1466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" hidden="1">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -1484,7 +1478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" hidden="1">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -1496,7 +1490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" hidden="1">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -1508,7 +1502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" hidden="1">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -1520,7 +1514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" hidden="1">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -1532,7 +1526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" hidden="1">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -1544,7 +1538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" hidden="1">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -1556,7 +1550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" hidden="1">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -1568,7 +1562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" hidden="1">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -1580,7 +1574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" hidden="1">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>67</v>
@@ -1592,7 +1586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" hidden="1">
       <c r="A70">
         <f t="shared" ref="A70:A102" si="1">A69+1</f>
         <v>68</v>
@@ -1604,7 +1598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" hidden="1">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -1616,7 +1610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" hidden="1">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -1631,7 +1625,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" hidden="1">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -1655,7 +1649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" hidden="1">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -1679,7 +1673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" hidden="1">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -1691,7 +1685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" hidden="1">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -1703,7 +1697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" hidden="1">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -1715,7 +1709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" hidden="1">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -1739,7 +1733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" hidden="1">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -1751,7 +1745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" hidden="1">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -1763,7 +1757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" hidden="1">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -1775,7 +1769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" hidden="1">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -1787,7 +1781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" hidden="1">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -1799,7 +1793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" hidden="1">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -1811,7 +1805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" hidden="1">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -1823,7 +1817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" hidden="1">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -1835,7 +1829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" hidden="1">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -1847,7 +1841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" hidden="1">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -1871,7 +1865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" hidden="1">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -1883,7 +1877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" hidden="1">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -1895,7 +1889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" hidden="1">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -1907,7 +1901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" hidden="1">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -1919,7 +1913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" hidden="1">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -1931,7 +1925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" hidden="1">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -1943,7 +1937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" hidden="1">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -1967,7 +1961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" hidden="1">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -1979,7 +1973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" hidden="1">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -1992,7 +1986,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C102" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:C102" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B102" xr:uid="{14B9F633-8D16-4C6A-BDBF-F784015327B4}">
@@ -3238,7 +3238,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C65"/>
+  <dimension ref="A2:C22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3253,220 +3253,229 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="A3">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+      <c r="A4">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="A5">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="A6">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="A7">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="A8">
+        <v>131</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="A9">
+        <v>132</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="A10">
+        <v>133</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="A11">
+        <v>134</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="A12">
+        <v>135</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="A13">
+        <v>136</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="A14">
+        <v>137</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="A15">
+        <v>138</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="2:3">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="2:3">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="2:3">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="2:3">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="2:3">
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25" spans="2:3">
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="2:3">
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27" spans="2:3">
-      <c r="B27" s="2"/>
-    </row>
-    <row r="28" spans="2:3">
-      <c r="B28" s="2"/>
-    </row>
-    <row r="29" spans="2:3">
-      <c r="B29" s="2"/>
-    </row>
-    <row r="30" spans="2:3">
-      <c r="B30" s="2"/>
-    </row>
-    <row r="31" spans="2:3">
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32" spans="2:3">
-      <c r="B32" s="2"/>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="2"/>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="2"/>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="2"/>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="2"/>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="2"/>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="2"/>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="2"/>
-    </row>
-    <row r="40" spans="2:2">
-      <c r="B40" s="2"/>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="2"/>
-    </row>
-    <row r="42" spans="2:2">
-      <c r="B42" s="2"/>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" s="2"/>
-    </row>
-    <row r="44" spans="2:2">
-      <c r="B44" s="2"/>
-    </row>
-    <row r="45" spans="2:2">
-      <c r="B45" s="2"/>
-    </row>
-    <row r="46" spans="2:2">
-      <c r="B46" s="2"/>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" s="2"/>
-    </row>
-    <row r="48" spans="2:2">
-      <c r="B48" s="2"/>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49" s="2"/>
-    </row>
-    <row r="50" spans="2:2">
-      <c r="B50" s="2"/>
-    </row>
-    <row r="51" spans="2:2">
-      <c r="B51" s="2"/>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52" s="2"/>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="2"/>
-    </row>
-    <row r="54" spans="2:2">
-      <c r="B54" s="2"/>
-    </row>
-    <row r="55" spans="2:2">
-      <c r="B55" s="2"/>
-    </row>
-    <row r="56" spans="2:2">
-      <c r="B56" s="2"/>
-    </row>
-    <row r="57" spans="2:2">
-      <c r="B57" s="2"/>
-    </row>
-    <row r="58" spans="2:2">
-      <c r="B58" s="2"/>
-    </row>
-    <row r="59" spans="2:2">
-      <c r="B59" s="2"/>
-    </row>
-    <row r="60" spans="2:2">
-      <c r="B60" s="2"/>
-    </row>
-    <row r="61" spans="2:2">
-      <c r="B61" s="2"/>
-    </row>
-    <row r="62" spans="2:2">
-      <c r="B62" s="2"/>
-    </row>
-    <row r="63" spans="2:2">
-      <c r="B63" s="2"/>
-    </row>
-    <row r="64" spans="2:2">
-      <c r="B64" s="2"/>
-    </row>
-    <row r="65" spans="2:2">
-      <c r="B65" s="2"/>
+      <c r="A16">
+        <v>139</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>140</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B18 B21:B24 B27:B29 B57:B60" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20:B23 B26:B28 B56:B59 B3:B17" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{170A8442-CEAA-4730-9A40-8967AA9214DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9692337E-ACC0-41E8-BB1E-CA369693A2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13305" yWindow="345" windowWidth="15780" windowHeight="14955" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8550" yWindow="525" windowWidth="15780" windowHeight="14955" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="60">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3238,7 +3238,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C22"/>
+  <dimension ref="A2:C31"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3472,10 +3472,109 @@
         <v>1</v>
       </c>
     </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>141</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>142</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>143</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>144</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>145</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>146</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>147</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>148</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>149</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20:B23 B26:B28 B56:B59 B3:B17" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B56:B59 B3:B17 B20:B32" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9692337E-ACC0-41E8-BB1E-CA369693A2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70DBC73-39AD-4D2E-B2E1-078469C51F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8550" yWindow="525" windowWidth="15780" windowHeight="14955" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="60">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3238,7 +3238,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C31"/>
+  <dimension ref="A2:C40"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3569,6 +3569,105 @@
       </c>
       <c r="C31">
         <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>144</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>145</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>146</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>147</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>148</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>149</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>150</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>151</v>
+      </c>
+      <c r="B39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>152</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70DBC73-39AD-4D2E-B2E1-078469C51F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A45A48-34F6-4571-B5D3-60E25BCDF1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="1305" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="60">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3238,7 +3238,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C40"/>
+  <dimension ref="A2:C53"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3670,10 +3670,153 @@
         <v>1</v>
       </c>
     </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>101</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>102</v>
+      </c>
+      <c r="B42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>103</v>
+      </c>
+      <c r="B43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>104</v>
+      </c>
+      <c r="B44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>105</v>
+      </c>
+      <c r="B45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>106</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>107</v>
+      </c>
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>108</v>
+      </c>
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>109</v>
+      </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>110</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>71</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>72</v>
+      </c>
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>73</v>
+      </c>
+      <c r="B53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B56:B59 B3:B17 B20:B32" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B56:B59 B3:B17 B20:B32 B41:B50" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A45A48-34F6-4571-B5D3-60E25BCDF1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77ABD3A-FFC2-4B6E-B676-496DD0D22544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="1305" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13065" yWindow="735" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="60">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3238,7 +3238,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C53"/>
+  <dimension ref="A2:C69"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3810,6 +3810,182 @@
         <v>9</v>
       </c>
       <c r="C53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>77</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>78</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>79</v>
+      </c>
+      <c r="B56" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>80</v>
+      </c>
+      <c r="B57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>81</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>82</v>
+      </c>
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>101</v>
+      </c>
+      <c r="B60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>102</v>
+      </c>
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>103</v>
+      </c>
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>104</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>105</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>106</v>
+      </c>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>107</v>
+      </c>
+      <c r="B66" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>108</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>109</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>110</v>
+      </c>
+      <c r="B69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69">
         <v>1</v>
       </c>
     </row>

--- a/toeic-test-v5/trial2-v2.xlsx
+++ b/toeic-test-v5/trial2-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77ABD3A-FFC2-4B6E-B676-496DD0D22544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5C6055-A0C2-4924-A075-499395B4A5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13065" yWindow="735" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="555" yWindow="0" windowWidth="13080" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="64">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -286,6 +286,25 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>over</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>にわたって</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>preference</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>好み</t>
+    <rPh sb="0" eb="1">
+      <t>コノ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -683,14 +702,14 @@
       </c>
       <c r="C6">
         <f>SUM(listening!C73:C102)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0.8666666666666667</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -770,7 +789,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1730,7 +1749,7 @@
         <v>10</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:3" hidden="1">
@@ -3238,7 +3257,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C69"/>
+  <dimension ref="A2:G82"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3934,7 +3953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>106</v>
       </c>
@@ -3945,7 +3964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>107</v>
       </c>
@@ -3956,7 +3975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>108</v>
       </c>
@@ -3967,7 +3986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>109</v>
       </c>
@@ -3978,7 +3997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>110</v>
       </c>
@@ -3987,6 +4006,161 @@
       </c>
       <c r="C69">
         <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70">
+        <v>89</v>
+      </c>
+      <c r="B70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71">
+        <v>90</v>
+      </c>
+      <c r="B71" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72">
+        <v>91</v>
+      </c>
+      <c r="B72" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73">
+        <v>111</v>
+      </c>
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74">
+        <v>112</v>
+      </c>
+      <c r="B74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75">
+        <v>113</v>
+      </c>
+      <c r="B75" t="s">
+        <v>9</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76">
+        <v>114</v>
+      </c>
+      <c r="B76" t="s">
+        <v>9</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77">
+        <v>115</v>
+      </c>
+      <c r="B77" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78">
+        <v>116</v>
+      </c>
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79">
+        <v>117</v>
+      </c>
+      <c r="B79" t="s">
+        <v>9</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="F79" t="s">
+        <v>62</v>
+      </c>
+      <c r="G79" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80">
+        <v>118</v>
+      </c>
+      <c r="B80" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81">
+        <v>119</v>
+      </c>
+      <c r="B81" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="F81" t="s">
+        <v>60</v>
+      </c>
+      <c r="G81" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82">
+        <v>120</v>
+      </c>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
